--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.576473218982953</v>
+        <v>1.06867689808473</v>
       </c>
       <c r="D2" t="n">
-        <v>40.37536295518306</v>
+        <v>6.560996480217247</v>
       </c>
       <c r="E2" t="n">
-        <v>14.9634756389525</v>
+        <v>2.431564791329782</v>
       </c>
       <c r="F2" t="n">
-        <v>1.828012423500198</v>
+        <v>0.2970520188187824</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.50342449688796</v>
+        <v>5.931806480744293</v>
       </c>
       <c r="D3" t="n">
-        <v>44.03138780218345</v>
+        <v>7.155100517854811</v>
       </c>
       <c r="E3" t="n">
-        <v>14.9634756389525</v>
+        <v>2.431564791329782</v>
       </c>
       <c r="F3" t="n">
-        <v>1.828012423500198</v>
+        <v>0.2970520188187824</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
